--- a/papers/paperCompare.xlsx
+++ b/papers/paperCompare.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MSC\thesis\papers\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tanvir all files\MSCThesisNK\papers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE1DFD85-FEF1-4A3F-A36B-E415DD1AAF00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC44993-27F8-44FE-BD2E-7FFD3268CC84}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -62,23 +61,209 @@
     <t>Open-Vocabulary Video Question Answering: A New Benchmark for Evaluating the Generalizability of Video Question Answering Models</t>
   </si>
   <si>
-    <t>The paper proposes an Open-Vocabulary VideoQA (OVQA) framework. Traditional VideoQA uses fixed-answer classification, but this paper introduces a GNN-based Soft Verbalizer to support rare and unseen answers. The method builds an answer graph where semantically similar answers are connected using external word knowledge. A Graph Neural Network (GNN) smooths answer embeddings by aggregating neighboring node information. The verbalizer function can be represented as: \n\nh_i^{(l+1)} = \sigma \left( \sum_{j \in \mathcal{N}(i)} W h_j^{(l)} \right) \n\nwhere neighboring answer nodes contribute semantic information to improve prediction of unseen answers. The framework also adds an answer encoder to existing VideoQA backbones such as EVQA and HCRN.</t>
-  </si>
-  <si>
-    <t>The benchmark is constructed from four major open-ended VideoQA datasets: \n\n• MSVD-QA → ~1,970 videos and ~50K QA pairs \n• MSRVTT-QA → ~10K videos and ~243K QA pairs \n• ActivityNet-QA → ~5.8K videos and ~58K QA pairs \n• TGIF-QA → GIF-based temporal QA benchmark \n\nThe authors reorganized these datasets into an open-vocabulary setting by separating answers into: \n1. Frequent answers \n2. Rare answers \n3. Unseen (OOV) answers \n\nThis creates a long-tail distribution closer to real-world conditions.</t>
-  </si>
-  <si>
-    <t>The paper reports that the proposed OVQA framework consistently improves baseline models across all datasets, especially on rare and unseen answers. The GNN soft verbalizer improved semantic generalization compared to standard classifiers. \n\nKey findings include: \n• Significant gain on OOV answer prediction \n• Better macro-average accuracy on long-tail distributions \n• Reduced bias toward frequent answers \n• Improvement across multiple VideoQA backbones \n\nFor example, HCRN + GNN verbalizer achieved higher OVQA performance than vanilla HCRN on MSVD-QA and MSRVTT-QA benchmarks. The improvement was strongest in unseen-answer evaluation splits rather than standard accuracy metrics. (CVF Open Access)</t>
-  </si>
-  <si>
     <t>The paper has several important limitations: \n\n1. The model still depends heavily on pretrained word embeddings and semantic proximity. If unseen answers are semantically distant from known answers, performance decreases. \n\n2. The GNN-based verbalizer increases computational overhead and graph-processing complexity. \n\n3. The framework improves answer generalization but does not deeply solve temporal reasoning problems in long videos. \n\n4. The benchmark mainly evaluates vocabulary generalization, not advanced causal reasoning or multi-step reasoning. \n\n5. The approach still relies on supervised QA datasets; therefore scalability to truly unlabeled video data remains limited. \n\n6. Accuracy gains are stronger on rare-answer subsets than on overall standard VideoQA accuracy, meaning the method specializes more in generalization than raw performance optimization. (CVF Open Access)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The paper proposes an Open-Vocabulary VideoQA (OVQA) framework. Traditional VideoQA uses fixed-answer classification, but this paper introduces a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>GNN-based Soft Verbalizer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to support rare and unseen answers. The method builds an answer graph where semantically similar answers are connected using external word knowledge. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A Graph Neural Network (GNN) smooths answer embeddings by aggregating neighboring node information.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The verbalizer function can be represented as: \n\nh_i^{(l+1)} = \sigma \left( \sum_{j \in \mathcal{N}(i)} W h_j^{(l)} \right) \n\nwhere neighboring answer nodes contribute semantic information to improve prediction of unseen answers. The framework also adds an answer encoder to existing VideoQA backbones such as EVQA and HCRN.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The benchmark is constructed from four major open-ended VideoQA datasets: \n\n• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MSVD-QA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → ~1,970 videos and ~50K QA pairs \n•</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> MSRVTT-QA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → ~10K videos and ~243K QA pairs \n• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ActivityNet-QA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → ~5.8K videos and ~58K QA pairs \n•</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> TGIF-QA </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>→ GIF-based temporal QA benchmark \n\nThe authors reorganized these datasets into an open-vocabulary setting by separating answers into: \n1. Frequent answers \n2. Rare answers \n3. Unseen (OOV) answers \n\nThis creates a long-tail distribution closer to real-world conditions.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The paper reports that the proposed </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">OVQA framework </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">consistently improves baseline models across all datasets, especially on rare and unseen answers. The GNN soft verbalizer improved semantic generalization compared to standard classifiers. \n\nKey findings include: \n• Significant gain on OOV answer prediction \n• Better macro-average accuracy on long-tail distributions \n• Reduced bias toward frequent answers \n• Improvement across multiple VideoQA backbones \n\nFor example, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>HCRN + GNN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> verbalizer achieved higher </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OVQA performance than vanilla HCRN on MSVD-QA and MSRVTT-QA benchmarks</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. The improvement was strongest in unseen-answer evaluation splits rather than standard accuracy metrics. (CVF Open Access)</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -92,6 +277,13 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -463,19 +655,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A75E0FBD-0A3D-4600-A1A0-92C1CC413B85}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="8.140625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="8.125" style="4" customWidth="1"/>
     <col min="2" max="2" width="29" style="4" customWidth="1"/>
-    <col min="3" max="3" width="48.140625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="48.125" style="4" customWidth="1"/>
     <col min="4" max="4" width="44" style="4" customWidth="1"/>
-    <col min="5" max="5" width="46.85546875" style="4" customWidth="1"/>
-    <col min="6" max="6" width="50.28515625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="46.875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="50.25" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="2" customFormat="1" ht="15">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
@@ -495,7 +687,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="1" customFormat="1" ht="285" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" s="1" customFormat="1" ht="242.25">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -503,19 +695,19 @@
         <v>6</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:6" s="1" customFormat="1">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -525,7 +717,7 @@
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
     </row>
-    <row r="4" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" s="1" customFormat="1">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -535,7 +727,7 @@
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
     </row>
-    <row r="5" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" s="1" customFormat="1">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -545,7 +737,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" s="1" customFormat="1">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -555,7 +747,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" s="1" customFormat="1">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -565,7 +757,7 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" s="1" customFormat="1">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -575,7 +767,7 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" s="1" customFormat="1">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -585,7 +777,7 @@
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
     </row>
-    <row r="10" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" s="1" customFormat="1">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -595,7 +787,7 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
     </row>
-    <row r="11" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" s="1" customFormat="1">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -607,5 +799,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>